--- a/automation/manifests/serving_tuning/automation_v0.xlsx
+++ b/automation/manifests/serving_tuning/automation_v0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wliao2\AppData\Local\Temp\Mxt211\RemoteFiles\7934362_8_0\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wliao2\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B535134-511C-4E13-A48C-78EE765A9F34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EFFF8A7-EB6B-4C5A-A6AB-D0856DE84570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="serving_tuning" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="128">
   <si>
     <t>enabled</t>
   </si>
@@ -80,9 +80,6 @@
     <t>meta-llama/Llama-3.1-8B-Instruct</t>
   </si>
   <si>
-    <t>/localdisk2</t>
-  </si>
-  <si>
     <t>/localdisk3</t>
   </si>
   <si>
@@ -122,9 +119,6 @@
     <t>meta-llama/Llama-4-Maverick-17B-128E-Instruct</t>
   </si>
   <si>
-    <t>/localdisk</t>
-  </si>
-  <si>
     <t>/localdisk1</t>
   </si>
   <si>
@@ -390,6 +384,27 @@
   </si>
   <si>
     <t>unsloth/gpt-oss-20b-BF16</t>
+  </si>
+  <si>
+    <t>/data</t>
+  </si>
+  <si>
+    <t>google/diffusiongemma-26B-A4B-it</t>
+  </si>
+  <si>
+    <t>RedHatAI/Qwen3-30B-A3B-Instruct-2507-quantized.w8a8</t>
+  </si>
+  <si>
+    <t>QuixiAI/Qwen3-30B-A3B-AWQ</t>
+  </si>
+  <si>
+    <t>Qwen/Qwen3-30B-A3B-GPTQ-Int4</t>
+  </si>
+  <si>
+    <t>RedHatAI/Qwen3-30B-A3B-quantized.w4a16</t>
+  </si>
+  <si>
+    <t>Qwen/Qwen3-30B-A3B-Instruct-2507-FP8</t>
   </si>
 </sst>
 </file>
@@ -488,7 +503,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -522,6 +537,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -824,11 +840,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R54"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:R60"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="45" customWidth="1"/>
+    <col min="2" max="2" width="52.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="20" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="5" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
@@ -843,7 +859,7 @@
     <col min="19" max="21" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -899,7 +915,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="b">
         <v>1</v>
       </c>
@@ -907,10 +923,10 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>121</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" s="5">
         <v>1</v>
@@ -922,17 +938,17 @@
         <v>6</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I2" s="2"/>
       <c r="J2" s="5">
         <v>7</v>
       </c>
       <c r="K2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" s="5" t="s">
         <v>22</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>23</v>
       </c>
       <c r="M2" s="5"/>
       <c r="N2" s="5">
@@ -949,18 +965,18 @@
       </c>
       <c r="R2" s="7"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="b">
         <v>1</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>121</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E3" s="5">
         <v>1</v>
@@ -972,17 +988,17 @@
         <v>6</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="5">
         <v>7</v>
       </c>
       <c r="K3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="5" t="s">
         <v>22</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>23</v>
       </c>
       <c r="M3" s="5"/>
       <c r="N3" s="5">
@@ -999,18 +1015,18 @@
       </c>
       <c r="R3" s="7"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="b">
         <v>1</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>121</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E4" s="5">
         <v>1</v>
@@ -1022,17 +1038,17 @@
         <v>6</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="5">
         <v>7</v>
       </c>
       <c r="K4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" s="5" t="s">
         <v>22</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>23</v>
       </c>
       <c r="M4" s="5"/>
       <c r="N4" s="5">
@@ -1049,18 +1065,18 @@
       </c>
       <c r="R4" s="7"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="b">
         <v>1</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>121</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E5" s="8">
         <v>4</v>
@@ -1072,17 +1088,17 @@
         <v>1</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="8">
         <v>7</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M5" s="8"/>
       <c r="N5" s="8">
@@ -1099,18 +1115,18 @@
       </c>
       <c r="R5" s="8"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>121</v>
       </c>
       <c r="D6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E6" s="10">
         <v>4</v>
@@ -1122,19 +1138,19 @@
         <v>1</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J6" s="10">
         <v>7</v>
       </c>
       <c r="K6" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="L6" s="10" t="s">
-        <v>23</v>
       </c>
       <c r="M6" s="10"/>
       <c r="N6" s="10">
@@ -1150,21 +1166,21 @@
         <v>99.74</v>
       </c>
       <c r="R6" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A7" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="B7" s="11" t="s">
+      <c r="C7" t="s">
+        <v>121</v>
+      </c>
+      <c r="D7" t="s">
         <v>32</v>
-      </c>
-      <c r="C7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" t="s">
-        <v>34</v>
       </c>
       <c r="E7" s="10">
         <v>4</v>
@@ -1176,17 +1192,17 @@
         <v>1</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="10">
         <v>7</v>
       </c>
       <c r="K7" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="L7" s="10" t="s">
-        <v>23</v>
       </c>
       <c r="M7" s="10"/>
       <c r="N7" s="10">
@@ -1203,18 +1219,18 @@
       </c>
       <c r="R7" s="10"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>121</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E8" s="10">
         <v>2</v>
@@ -1226,17 +1242,17 @@
         <v>2</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="10">
         <v>7</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M8" s="10"/>
       <c r="N8" s="10">
@@ -1253,18 +1269,18 @@
       </c>
       <c r="R8" s="10"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>121</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E9" s="10">
         <v>4</v>
@@ -1276,17 +1292,17 @@
         <v>1</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="10">
         <v>7</v>
       </c>
       <c r="K9" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="L9" s="10" t="s">
-        <v>23</v>
       </c>
       <c r="M9" s="10"/>
       <c r="N9" s="10">
@@ -1303,18 +1319,18 @@
       </c>
       <c r="R9" s="10"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>121</v>
       </c>
       <c r="D10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E10" s="10">
         <v>1</v>
@@ -1326,17 +1342,17 @@
         <v>6</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="10">
         <v>7</v>
       </c>
       <c r="K10" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="L10" s="10" t="s">
-        <v>23</v>
       </c>
       <c r="M10" s="10"/>
       <c r="N10" s="10">
@@ -1353,18 +1369,18 @@
       </c>
       <c r="R10" s="10"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>121</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E11" s="10">
         <v>1</v>
@@ -1376,17 +1392,17 @@
         <v>6</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="10">
         <v>7</v>
       </c>
       <c r="K11" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="L11" s="10" t="s">
-        <v>23</v>
       </c>
       <c r="M11" s="10"/>
       <c r="N11" s="10">
@@ -1403,18 +1419,18 @@
       </c>
       <c r="R11" s="10"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C12" t="s">
-        <v>19</v>
+        <v>121</v>
       </c>
       <c r="D12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E12" s="10">
         <v>2</v>
@@ -1426,17 +1442,17 @@
         <v>2</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="10">
         <v>7</v>
       </c>
       <c r="K12" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="L12" s="10" t="s">
-        <v>23</v>
       </c>
       <c r="M12" s="10"/>
       <c r="N12" s="10">
@@ -1453,18 +1469,18 @@
       </c>
       <c r="R12" s="10"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>121</v>
       </c>
       <c r="D13" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E13" s="10">
         <v>1</v>
@@ -1476,17 +1492,17 @@
         <v>6</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="10">
         <v>7</v>
       </c>
       <c r="K13" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L13" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="L13" s="10" t="s">
-        <v>23</v>
       </c>
       <c r="M13" s="10"/>
       <c r="N13" s="10">
@@ -1503,18 +1519,18 @@
       </c>
       <c r="R13" s="10"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>121</v>
       </c>
       <c r="D14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E14" s="10">
         <v>1</v>
@@ -1526,24 +1542,24 @@
         <v>6</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J14" s="10">
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
+        <v>121</v>
       </c>
       <c r="D15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E15" s="10">
         <v>1</v>
@@ -1555,24 +1571,24 @@
         <v>6</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J15" s="10">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
+        <v>121</v>
       </c>
       <c r="D16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E16" s="10">
         <v>2</v>
@@ -1584,24 +1600,24 @@
         <v>2</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J16" s="10">
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C17" t="s">
-        <v>19</v>
+        <v>121</v>
       </c>
       <c r="D17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E17" s="10">
         <v>2</v>
@@ -1613,17 +1629,17 @@
         <v>2</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I17" s="2"/>
       <c r="J17" s="10">
         <v>7</v>
       </c>
       <c r="K17" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L17" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="L17" s="10" t="s">
-        <v>23</v>
       </c>
       <c r="M17" s="10"/>
       <c r="N17" s="10">
@@ -1640,18 +1656,18 @@
       </c>
       <c r="R17" s="10"/>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C18" t="s">
-        <v>19</v>
+        <v>121</v>
       </c>
       <c r="D18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E18" s="10">
         <v>1</v>
@@ -1663,17 +1679,17 @@
         <v>6</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I18" s="2"/>
       <c r="J18" s="10">
         <v>7</v>
       </c>
       <c r="K18" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L18" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="L18" s="10" t="s">
-        <v>23</v>
       </c>
       <c r="M18" s="10"/>
       <c r="N18" s="10">
@@ -1690,18 +1706,18 @@
       </c>
       <c r="R18" s="10"/>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C19" t="s">
-        <v>19</v>
+        <v>121</v>
       </c>
       <c r="D19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E19" s="10">
         <v>2</v>
@@ -1713,17 +1729,17 @@
         <v>2</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I19" s="2"/>
       <c r="J19" s="10">
         <v>7</v>
       </c>
       <c r="K19" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L19" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="L19" s="10" t="s">
-        <v>23</v>
       </c>
       <c r="M19" s="10"/>
       <c r="N19" s="10">
@@ -1740,18 +1756,18 @@
       </c>
       <c r="R19" s="10"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C20" t="s">
-        <v>19</v>
+        <v>121</v>
       </c>
       <c r="D20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E20" s="10">
         <v>2</v>
@@ -1763,17 +1779,17 @@
         <v>2</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I20" s="2"/>
       <c r="J20" s="10">
         <v>7</v>
       </c>
       <c r="K20" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L20" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="L20" s="10" t="s">
-        <v>23</v>
       </c>
       <c r="M20" s="10"/>
       <c r="N20" s="10">
@@ -1790,18 +1806,18 @@
       </c>
       <c r="R20" s="10"/>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C21" t="s">
-        <v>33</v>
+        <v>121</v>
       </c>
       <c r="D21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E21" s="10">
         <v>2</v>
@@ -1813,19 +1829,19 @@
         <v>2</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="J21" s="10">
         <v>7</v>
       </c>
       <c r="K21" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L21" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="L21" s="10" t="s">
-        <v>23</v>
       </c>
       <c r="M21" s="10"/>
       <c r="N21" s="10">
@@ -1841,21 +1857,21 @@
         <v>99.6</v>
       </c>
       <c r="R21" s="10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C22" t="s">
-        <v>33</v>
+        <v>121</v>
       </c>
       <c r="D22" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E22" s="10">
         <v>1</v>
@@ -1867,17 +1883,17 @@
         <v>6</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I22" s="2"/>
       <c r="J22" s="10">
         <v>7</v>
       </c>
       <c r="K22" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L22" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="L22" s="10" t="s">
-        <v>23</v>
       </c>
       <c r="M22" s="10"/>
       <c r="N22" s="10">
@@ -1894,18 +1910,18 @@
       </c>
       <c r="R22" s="10"/>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C23" t="s">
-        <v>33</v>
+        <v>121</v>
       </c>
       <c r="D23" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E23" s="10">
         <v>1</v>
@@ -1917,17 +1933,17 @@
         <v>6</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I23" s="2"/>
       <c r="J23" s="10">
         <v>7</v>
       </c>
       <c r="K23" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L23" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="L23" s="10" t="s">
-        <v>23</v>
       </c>
       <c r="M23" s="10"/>
       <c r="N23" s="10">
@@ -1944,18 +1960,18 @@
       </c>
       <c r="R23" s="10"/>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C24" t="s">
-        <v>33</v>
+        <v>121</v>
       </c>
       <c r="D24" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E24" s="10">
         <v>1</v>
@@ -1967,17 +1983,17 @@
         <v>6</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I24" s="2"/>
       <c r="J24" s="10">
         <v>7</v>
       </c>
       <c r="K24" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L24" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="L24" s="10" t="s">
-        <v>23</v>
       </c>
       <c r="M24" s="10"/>
       <c r="N24" s="10">
@@ -1994,18 +2010,18 @@
       </c>
       <c r="R24" s="10"/>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C25" t="s">
-        <v>33</v>
+        <v>121</v>
       </c>
       <c r="D25" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E25" s="10">
         <v>1</v>
@@ -2017,17 +2033,17 @@
         <v>6</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I25" s="2"/>
       <c r="J25" s="10">
         <v>7</v>
       </c>
       <c r="K25" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L25" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="L25" s="10" t="s">
-        <v>23</v>
       </c>
       <c r="M25" s="10"/>
       <c r="N25" s="10">
@@ -2044,18 +2060,18 @@
       </c>
       <c r="R25" s="10"/>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C26" t="s">
-        <v>19</v>
+        <v>121</v>
       </c>
       <c r="D26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E26" s="10">
         <v>1</v>
@@ -2067,17 +2083,17 @@
         <v>6</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I26" s="2"/>
       <c r="J26" s="10">
         <v>7</v>
       </c>
       <c r="K26" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L26" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="L26" s="10" t="s">
-        <v>23</v>
       </c>
       <c r="M26" s="10"/>
       <c r="N26" s="10">
@@ -2094,18 +2110,18 @@
       </c>
       <c r="R26" s="10"/>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C27" t="s">
-        <v>33</v>
+        <v>121</v>
       </c>
       <c r="D27" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E27" s="10">
         <v>1</v>
@@ -2117,17 +2133,17 @@
         <v>6</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I27" s="2"/>
       <c r="J27" s="10">
         <v>7</v>
       </c>
       <c r="K27" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L27" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="L27" s="10" t="s">
-        <v>23</v>
       </c>
       <c r="M27" s="10"/>
       <c r="N27" s="10">
@@ -2144,18 +2160,18 @@
       </c>
       <c r="R27" s="10"/>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C28" t="s">
-        <v>33</v>
+        <v>121</v>
       </c>
       <c r="D28" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E28" s="10">
         <v>1</v>
@@ -2167,17 +2183,17 @@
         <v>6</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I28" s="2"/>
       <c r="J28" s="10">
         <v>7</v>
       </c>
       <c r="K28" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L28" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="L28" s="10" t="s">
-        <v>23</v>
       </c>
       <c r="M28" s="10"/>
       <c r="N28" s="10">
@@ -2194,18 +2210,18 @@
       </c>
       <c r="R28" s="10"/>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C29" t="s">
-        <v>20</v>
+        <v>121</v>
       </c>
       <c r="D29" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E29" s="10">
         <v>2</v>
@@ -2217,17 +2233,17 @@
         <v>2</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I29" s="2"/>
       <c r="J29" s="10">
         <v>7</v>
       </c>
       <c r="K29" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L29" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="L29" s="10" t="s">
-        <v>23</v>
       </c>
       <c r="M29" s="10"/>
       <c r="N29" s="10">
@@ -2243,21 +2259,21 @@
         <v>99.65</v>
       </c>
       <c r="R29" s="10" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.35">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C30" t="s">
-        <v>20</v>
+        <v>121</v>
       </c>
       <c r="D30" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E30" s="10">
         <v>2</v>
@@ -2269,17 +2285,17 @@
         <v>2</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I30" s="2"/>
       <c r="J30" s="10">
         <v>7</v>
       </c>
       <c r="K30" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L30" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="L30" s="10" t="s">
-        <v>23</v>
       </c>
       <c r="M30" s="10"/>
       <c r="N30" s="10">
@@ -2295,21 +2311,21 @@
         <v>99.65</v>
       </c>
       <c r="R30" s="10" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.35">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C31" t="s">
-        <v>19</v>
+        <v>121</v>
       </c>
       <c r="D31" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E31" s="10">
         <v>1</v>
@@ -2321,17 +2337,17 @@
         <v>6</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I31" s="2"/>
       <c r="J31" s="10">
         <v>7</v>
       </c>
       <c r="K31" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L31" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="L31" s="10" t="s">
-        <v>23</v>
       </c>
       <c r="M31" s="10"/>
       <c r="N31" s="10">
@@ -2347,21 +2363,21 @@
         <v>86.51</v>
       </c>
       <c r="R31" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.35">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C32" t="s">
-        <v>20</v>
+        <v>121</v>
       </c>
       <c r="D32" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E32" s="10">
         <v>1</v>
@@ -2373,17 +2389,17 @@
         <v>6</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I32" s="2"/>
       <c r="J32" s="10">
         <v>7</v>
       </c>
       <c r="K32" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L32" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="L32" s="10" t="s">
-        <v>23</v>
       </c>
       <c r="M32" s="10"/>
       <c r="N32" s="10">
@@ -2400,18 +2416,18 @@
       </c>
       <c r="R32" s="10"/>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C33" t="s">
-        <v>19</v>
+        <v>121</v>
       </c>
       <c r="D33" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E33" s="10">
         <v>1</v>
@@ -2423,17 +2439,17 @@
         <v>6</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I33" s="2"/>
       <c r="J33" s="10">
         <v>7</v>
       </c>
       <c r="K33" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L33" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="L33" s="10" t="s">
-        <v>23</v>
       </c>
       <c r="M33" s="10"/>
       <c r="N33" s="10">
@@ -2450,18 +2466,18 @@
       </c>
       <c r="R33" s="10"/>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C34" t="s">
-        <v>19</v>
+        <v>121</v>
       </c>
       <c r="D34" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E34" s="10">
         <v>1</v>
@@ -2473,17 +2489,17 @@
         <v>6</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I34" s="2"/>
       <c r="J34" s="10">
         <v>7</v>
       </c>
       <c r="K34" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L34" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="L34" s="10" t="s">
-        <v>23</v>
       </c>
       <c r="M34" s="10"/>
       <c r="N34" s="10">
@@ -2500,18 +2516,18 @@
       </c>
       <c r="R34" s="10"/>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C35" t="s">
-        <v>33</v>
+        <v>121</v>
       </c>
       <c r="D35" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E35" s="10">
         <v>2</v>
@@ -2523,17 +2539,17 @@
         <v>2</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I35" s="2"/>
       <c r="J35" s="10">
         <v>7</v>
       </c>
       <c r="K35" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L35" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M35" s="10"/>
       <c r="N35" s="10">
@@ -2550,18 +2566,18 @@
       </c>
       <c r="R35" s="10"/>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C36" t="s">
-        <v>19</v>
+        <v>121</v>
       </c>
       <c r="D36" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E36" s="10">
         <v>2</v>
@@ -2573,17 +2589,17 @@
         <v>2</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I36" s="2"/>
       <c r="J36" s="10">
         <v>7</v>
       </c>
       <c r="K36" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L36" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="L36" s="10" t="s">
-        <v>23</v>
       </c>
       <c r="M36" s="10"/>
       <c r="N36" s="10">
@@ -2600,18 +2616,18 @@
       </c>
       <c r="R36" s="10"/>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C37" t="s">
-        <v>33</v>
+        <v>121</v>
       </c>
       <c r="D37" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E37" s="10">
         <v>1</v>
@@ -2623,17 +2639,17 @@
         <v>6</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I37" s="2"/>
       <c r="J37" s="10">
         <v>7</v>
       </c>
       <c r="K37" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L37" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="L37" s="10" t="s">
-        <v>23</v>
       </c>
       <c r="M37" s="10"/>
       <c r="N37" s="10">
@@ -2650,18 +2666,18 @@
       </c>
       <c r="R37" s="10"/>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C38" t="s">
-        <v>33</v>
+        <v>121</v>
       </c>
       <c r="D38" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E38" s="10">
         <v>4</v>
@@ -2673,24 +2689,24 @@
         <v>1</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J38" s="10">
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="b">
         <v>0</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C39" t="s">
-        <v>33</v>
+        <v>121</v>
       </c>
       <c r="D39" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E39" s="10">
         <v>4</v>
@@ -2702,24 +2718,24 @@
         <v>1</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J39" s="10">
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="b">
         <v>0</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C40" t="s">
-        <v>33</v>
+        <v>121</v>
       </c>
       <c r="D40" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E40" s="10">
         <v>4</v>
@@ -2731,24 +2747,24 @@
         <v>1</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J40" s="10">
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C41" t="s">
-        <v>33</v>
+        <v>121</v>
       </c>
       <c r="D41" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E41" s="10">
         <v>4</v>
@@ -2760,24 +2776,24 @@
         <v>1</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J41" s="10">
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C42" t="s">
-        <v>33</v>
+        <v>121</v>
       </c>
       <c r="D42" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E42" s="10">
         <v>1</v>
@@ -2789,24 +2805,24 @@
         <v>6</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J42" s="10">
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C43" t="s">
-        <v>33</v>
+        <v>121</v>
       </c>
       <c r="D43" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E43" s="10">
         <v>2</v>
@@ -2818,25 +2834,25 @@
         <v>2</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J43" s="10">
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B44" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="C44" t="s">
+        <v>121</v>
+      </c>
+      <c r="D44" t="s">
         <v>118</v>
       </c>
-      <c r="C44" t="s">
-        <v>33</v>
-      </c>
-      <c r="D44" t="s">
-        <v>120</v>
-      </c>
       <c r="E44" s="10">
         <v>2</v>
       </c>
@@ -2847,24 +2863,24 @@
         <v>2</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J44" s="10">
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="b">
         <v>0</v>
       </c>
       <c r="B45" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="C45" t="s">
+        <v>121</v>
+      </c>
+      <c r="D45" t="s">
         <v>119</v>
-      </c>
-      <c r="C45" t="s">
-        <v>33</v>
-      </c>
-      <c r="D45" t="s">
-        <v>121</v>
       </c>
       <c r="E45" s="10">
         <v>4</v>
@@ -2876,24 +2892,24 @@
         <v>1</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J45" s="10">
         <v>7</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C46" t="s">
-        <v>19</v>
+        <v>121</v>
       </c>
       <c r="D46" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E46" s="10">
         <v>1</v>
@@ -2905,17 +2921,17 @@
         <v>6</v>
       </c>
       <c r="H46" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I46" s="2"/>
       <c r="J46" s="10">
         <v>7</v>
       </c>
       <c r="K46" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L46" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="L46" s="10" t="s">
-        <v>23</v>
       </c>
       <c r="M46" s="10"/>
       <c r="N46" s="10">
@@ -2932,18 +2948,18 @@
       </c>
       <c r="R46" s="10"/>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C47" t="s">
-        <v>19</v>
+        <v>121</v>
       </c>
       <c r="D47" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E47" s="10">
         <v>1</v>
@@ -2955,17 +2971,17 @@
         <v>6</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I47" s="2"/>
       <c r="J47" s="10">
         <v>7</v>
       </c>
       <c r="K47" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L47" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="L47" s="10" t="s">
-        <v>23</v>
       </c>
       <c r="M47" s="10"/>
       <c r="N47" s="10">
@@ -2982,18 +2998,18 @@
       </c>
       <c r="R47" s="10"/>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C48" t="s">
-        <v>19</v>
+        <v>121</v>
       </c>
       <c r="D48" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E48" s="10">
         <v>1</v>
@@ -3005,17 +3021,17 @@
         <v>6</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I48" s="2"/>
       <c r="J48" s="10">
         <v>7</v>
       </c>
       <c r="K48" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L48" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="L48" s="10" t="s">
-        <v>23</v>
       </c>
       <c r="M48" s="10"/>
       <c r="N48" s="10">
@@ -3032,18 +3048,18 @@
       </c>
       <c r="R48" s="10"/>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C49" t="s">
-        <v>19</v>
+        <v>121</v>
       </c>
       <c r="D49" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E49" s="10">
         <v>2</v>
@@ -3055,19 +3071,19 @@
         <v>2</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J49" s="10">
         <v>7</v>
       </c>
       <c r="K49" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L49" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M49" s="10"/>
       <c r="N49" s="10">
@@ -3083,21 +3099,21 @@
         <v>137.84</v>
       </c>
       <c r="R49" s="10" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.35">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C50" t="s">
-        <v>19</v>
+        <v>121</v>
       </c>
       <c r="D50" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E50" s="10">
         <v>2</v>
@@ -3109,17 +3125,17 @@
         <v>2</v>
       </c>
       <c r="H50" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I50" s="2"/>
       <c r="J50" s="10">
         <v>7</v>
       </c>
       <c r="K50" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L50" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="L50" s="10" t="s">
-        <v>23</v>
       </c>
       <c r="M50" s="10"/>
       <c r="N50" s="10">
@@ -3136,18 +3152,18 @@
       </c>
       <c r="R50" s="10"/>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C51" t="s">
-        <v>19</v>
+        <v>121</v>
       </c>
       <c r="D51" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E51" s="10">
         <v>1</v>
@@ -3159,17 +3175,17 @@
         <v>6</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I51" s="2"/>
       <c r="J51" s="10">
         <v>7</v>
       </c>
       <c r="K51" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L51" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="L51" s="10" t="s">
-        <v>23</v>
       </c>
       <c r="M51" s="10"/>
       <c r="N51" s="10">
@@ -3186,18 +3202,18 @@
       </c>
       <c r="R51" s="10"/>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C52" t="s">
-        <v>33</v>
+        <v>121</v>
       </c>
       <c r="D52" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E52" s="10">
         <v>1</v>
@@ -3209,17 +3225,17 @@
         <v>6</v>
       </c>
       <c r="H52" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I52" s="2"/>
       <c r="J52" s="10">
         <v>7</v>
       </c>
       <c r="K52" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L52" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="L52" s="10" t="s">
-        <v>23</v>
       </c>
       <c r="M52" s="10"/>
       <c r="N52" s="10">
@@ -3236,18 +3252,18 @@
       </c>
       <c r="R52" s="10"/>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C53" t="s">
-        <v>33</v>
+        <v>121</v>
       </c>
       <c r="D53" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E53" s="10">
         <v>1</v>
@@ -3259,17 +3275,17 @@
         <v>6</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I53" s="2"/>
       <c r="J53" s="10">
         <v>7</v>
       </c>
       <c r="K53" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L53" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="L53" s="10" t="s">
-        <v>23</v>
       </c>
       <c r="M53" s="10"/>
       <c r="N53" s="10">
@@ -3286,18 +3302,18 @@
       </c>
       <c r="R53" s="10"/>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="b">
         <v>1</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C54" t="s">
-        <v>33</v>
+        <v>121</v>
       </c>
       <c r="D54" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E54" s="10">
         <v>1</v>
@@ -3309,17 +3325,17 @@
         <v>6</v>
       </c>
       <c r="H54" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I54" s="2"/>
       <c r="J54" s="10">
         <v>7</v>
       </c>
       <c r="K54" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L54" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="L54" s="10" t="s">
-        <v>23</v>
       </c>
       <c r="M54" s="10"/>
       <c r="N54" s="10">
@@ -3335,6 +3351,180 @@
         <v>37.299999999999997</v>
       </c>
       <c r="R54" s="10"/>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A55" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="B55" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="C55" t="s">
+        <v>121</v>
+      </c>
+      <c r="D55" t="s">
+        <v>19</v>
+      </c>
+      <c r="E55" s="10">
+        <v>2</v>
+      </c>
+      <c r="F55" s="10">
+        <v>1</v>
+      </c>
+      <c r="G55" s="10">
+        <v>2</v>
+      </c>
+      <c r="H55" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J55" s="10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A56" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="B56" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="C56" t="s">
+        <v>121</v>
+      </c>
+      <c r="D56" t="s">
+        <v>19</v>
+      </c>
+      <c r="E56" s="10">
+        <v>2</v>
+      </c>
+      <c r="F56" s="10">
+        <v>1</v>
+      </c>
+      <c r="G56" s="10">
+        <v>2</v>
+      </c>
+      <c r="H56" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J56" s="10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A57" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="B57" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="C57" t="s">
+        <v>121</v>
+      </c>
+      <c r="D57" t="s">
+        <v>19</v>
+      </c>
+      <c r="E57" s="10">
+        <v>2</v>
+      </c>
+      <c r="F57" s="10">
+        <v>1</v>
+      </c>
+      <c r="G57" s="10">
+        <v>2</v>
+      </c>
+      <c r="H57" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J57" s="10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A58" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="B58" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="C58" t="s">
+        <v>121</v>
+      </c>
+      <c r="D58" t="s">
+        <v>19</v>
+      </c>
+      <c r="E58" s="10">
+        <v>2</v>
+      </c>
+      <c r="F58" s="10">
+        <v>1</v>
+      </c>
+      <c r="G58" s="10">
+        <v>2</v>
+      </c>
+      <c r="H58" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J58" s="10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A59" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="B59" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="C59" t="s">
+        <v>121</v>
+      </c>
+      <c r="D59" t="s">
+        <v>19</v>
+      </c>
+      <c r="E59" s="10">
+        <v>2</v>
+      </c>
+      <c r="F59" s="10">
+        <v>1</v>
+      </c>
+      <c r="G59" s="10">
+        <v>2</v>
+      </c>
+      <c r="H59" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J59" s="10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A60" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="B60" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="C60" t="s">
+        <v>121</v>
+      </c>
+      <c r="D60" t="s">
+        <v>19</v>
+      </c>
+      <c r="E60" s="10">
+        <v>2</v>
+      </c>
+      <c r="F60" s="10">
+        <v>1</v>
+      </c>
+      <c r="G60" s="10">
+        <v>2</v>
+      </c>
+      <c r="H60" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J60" s="10">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
@@ -3345,253 +3535,253 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>80</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="B2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="C2" t="s">
         <v>82</v>
       </c>
-      <c r="B2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="B3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" t="s">
         <v>83</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C5" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>87</v>
-      </c>
-      <c r="B5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C5" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>83</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="B10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>93</v>
       </c>
-      <c r="B10" t="s">
-        <v>83</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="B11" t="s">
+        <v>81</v>
+      </c>
+      <c r="C11" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>95</v>
       </c>
-      <c r="B11" t="s">
-        <v>83</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="B12" t="s">
+        <v>81</v>
+      </c>
+      <c r="C12" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>97</v>
       </c>
-      <c r="B12" t="s">
-        <v>83</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="B13" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>99</v>
-      </c>
-      <c r="B13" t="s">
-        <v>83</v>
-      </c>
-      <c r="C13" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>11</v>
       </c>
       <c r="B16" t="s">
+        <v>100</v>
+      </c>
+      <c r="C16" t="s">
         <v>102</v>
       </c>
-      <c r="C16" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C17" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C18" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C19" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C20" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>16</v>
       </c>
       <c r="B21" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C21" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
